--- a/data/appliances_2_4.xlsx
+++ b/data/appliances_2_4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stuja\OneDrive\Dokumenter\Studie\0. Etterstudium\Eninf Oblig 1\git2\in5410_intelligent_load_scheduling\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA5EB95E-007D-449F-8A85-2EBBAAE2C2DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E2E397C-1A09-4094-9BD1-A0DA4EA7DF48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -549,7 +549,7 @@
     <col min="2" max="2" width="14" style="6" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="16.42578125" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
     <col min="7" max="7" width="14.28515625" customWidth="1"/>
     <col min="8" max="8" width="11.5703125" customWidth="1"/>
